--- a/plantillas/106.xlsx
+++ b/plantillas/106.xlsx
@@ -31,7 +31,7 @@
     <definedName name="MARCA_17">Listas!$T$2:$T$37</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$3</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$9</definedName>
-    <definedName name="MARCA_20">Listas!$W$2:$W$27</definedName>
+    <definedName name="MARCA_20">Listas!$W$2:$W$26</definedName>
     <definedName name="MARCA_21">Listas!$X$2:$X$15</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$2</definedName>
     <definedName name="MARCA_23">Listas!$Z$2:$Z$2</definedName>
@@ -644,11 +644,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B3,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B3,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B3,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B3,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -668,11 +668,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B4,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B4,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B4,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B4,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -692,11 +692,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B5,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B5,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B5,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B5,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -716,11 +716,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B6,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B6,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B6,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B6,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -735,11 +735,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B7,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B7,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B7,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B7,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -754,11 +754,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B8,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B8,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B8,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B8,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -773,11 +773,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B9,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B9,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B9,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B9,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -792,11 +792,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B10,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B10,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B10,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B10,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -811,11 +811,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B11,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B11,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B11,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B11,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -830,11 +830,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B12,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B12,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B12,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B12,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -849,11 +849,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B13,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B13,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B13,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B13,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -868,11 +868,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B14,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B14,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B14,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B14,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -887,11 +887,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B15,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B15,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B15,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B15,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -906,11 +906,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B16,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B16,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B16,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B16,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -925,11 +925,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B17,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B17,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B17,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B17,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -944,11 +944,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B18,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B18,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B18,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B18,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -963,11 +963,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B19,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B19,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B19,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B19,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -982,11 +982,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B20,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B20,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B20,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B20,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1001,11 +1001,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B21,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B21,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B21,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B21,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1020,11 +1020,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B22,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B22,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B22,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B22,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1039,11 +1039,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B23,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B23,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B23,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B23,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1058,11 +1058,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B24,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B24,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B24,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B24,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1077,11 +1077,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B25,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B25,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B25,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B25,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1096,11 +1096,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B26,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B26,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B26,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B26,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1115,11 +1115,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B27,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B27,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B27,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B27,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1134,11 +1134,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B28,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B28,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B28,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B28,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1153,11 +1153,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B29,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B29,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B29,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B29,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1172,11 +1172,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B30,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B30,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B30,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B30,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1191,11 +1191,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B31,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B31,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B31,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B31,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1210,11 +1210,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B32,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B32,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B32,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B32,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1229,11 +1229,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B33,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B33,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B33,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B33,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1248,11 +1248,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B34,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B34,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B34,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B34,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1267,11 +1267,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B35,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B35,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B35,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B35,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1286,11 +1286,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B36,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B36,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B36,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B36,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1305,11 +1305,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B37,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B37,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B37,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B37,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1324,11 +1324,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B38,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B38,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B38,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B38,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1343,11 +1343,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B39,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B39,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B39,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B39,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1362,11 +1362,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B40,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B40,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B40,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B40,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1381,11 +1381,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B41,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B41,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B41,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B41,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1400,11 +1400,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B42,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B42,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B42,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B42,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1419,11 +1419,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B43,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B43,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B43,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B43,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1438,11 +1438,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B44,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B44,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B44,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B44,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1457,11 +1457,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B45,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B45,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B45,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B45,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1476,11 +1476,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B46,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B46,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B46,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B46,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1495,11 +1495,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B47,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B47,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B47,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B47,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1514,11 +1514,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B48,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B48,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B48,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B48,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1533,11 +1533,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B49,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B49,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B49,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B49,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1552,11 +1552,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B50,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B50,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B50,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B50,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1571,11 +1571,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B51,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B51,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B51,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B51,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1590,11 +1590,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B52,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B52,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B52,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B52,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1609,11 +1609,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B53,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B53,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B53,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B53,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1628,11 +1628,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B54,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B54,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B54,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B54,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1647,11 +1647,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B55,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B55,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B55,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B55,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1666,11 +1666,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B56,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B56,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B56,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B56,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1685,11 +1685,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B57,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B57,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B57,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B57,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1704,11 +1704,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B58,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B58,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B58,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B58,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1723,11 +1723,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B59,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B59,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B59,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B59,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1742,11 +1742,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B60,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B60,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B60,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B60,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1761,11 +1761,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B61,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B61,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B61,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B61,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1780,11 +1780,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B62,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B62,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B62,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B62,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1799,11 +1799,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B63,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B63,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B63,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B63,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1818,11 +1818,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B64,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B64,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B64,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B64,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1837,11 +1837,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B65,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B65,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B65,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B65,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1856,11 +1856,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B66,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B66,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B66,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B66,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1875,11 +1875,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B67,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B67,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B67,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B67,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1894,11 +1894,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B68,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B68,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B68,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B68,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1913,11 +1913,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B69,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B69,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B69,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B69,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1932,11 +1932,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B70,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B70,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B70,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B70,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1951,11 +1951,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B71,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B71,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B71,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B71,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1970,11 +1970,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B72,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B72,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B72,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B72,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1989,11 +1989,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B73,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B73,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B73,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B73,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2008,11 +2008,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B74,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B74,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B74,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B74,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2027,11 +2027,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B75,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B75,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B75,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B75,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2046,11 +2046,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B76,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B76,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B76,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B76,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2065,11 +2065,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B77,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B77,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B77,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B77,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2084,11 +2084,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B78,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B78,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B78,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B78,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2103,11 +2103,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B79,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B79,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B79,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B79,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2122,11 +2122,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B80,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B80,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B80,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B80,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2141,11 +2141,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B81,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B81,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B81,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B81,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2160,11 +2160,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B82,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B82,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B82,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B82,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2179,11 +2179,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B83,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B83,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B83,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B83,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2198,11 +2198,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B84,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B84,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B84,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B84,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2217,11 +2217,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B85,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B85,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B85,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B85,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2236,11 +2236,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B86,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B86,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B86,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B86,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2255,11 +2255,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B87,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B87,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B87,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B87,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2274,11 +2274,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B88,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B88,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B88,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B88,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2293,11 +2293,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B89,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B89,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B89,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B89,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2312,11 +2312,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B90,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B90,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B90,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B90,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2331,11 +2331,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B91,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B91,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B91,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B91,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2350,11 +2350,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B92,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B92,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B92,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B92,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2369,11 +2369,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B93,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B93,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B93,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B93,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2388,11 +2388,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B94,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B94,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B94,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B94,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2407,11 +2407,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B95,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B95,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B95,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B95,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2426,11 +2426,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B96,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B96,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B96,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B96,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2445,11 +2445,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B97,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B97,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B97,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B97,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2464,11 +2464,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B98,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B98,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B98,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B98,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2483,11 +2483,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B99,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B99,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B99,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B99,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2502,11 +2502,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B100,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B100,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B100,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B100,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2521,11 +2521,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B101,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B101,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B101,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B101,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2540,11 +2540,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B102,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B102,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B102,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B102,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2559,11 +2559,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B103,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B103,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B103,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B103,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2578,11 +2578,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B104,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B104,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B104,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B104,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2597,11 +2597,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B105,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B105,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B105,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B105,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2616,11 +2616,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B106,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B106,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B106,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B106,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2635,11 +2635,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B107,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B107,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B107,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B107,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2654,11 +2654,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B108,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B108,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B108,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B108,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2673,11 +2673,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B109,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B109,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B109,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B109,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2692,11 +2692,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B110,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B110,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B110,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B110,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2711,11 +2711,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B111,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B111,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B111,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B111,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2730,11 +2730,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B112,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B112,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B112,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B112,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2749,11 +2749,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B113,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B113,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B113,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B113,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2768,11 +2768,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B114,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B114,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B114,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B114,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2787,11 +2787,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B115,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B115,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B115,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B115,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2806,11 +2806,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B116,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B116,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B116,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B116,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2825,11 +2825,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B117,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B117,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B117,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B117,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2844,11 +2844,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B118,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B118,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B118,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B118,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2863,11 +2863,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B119,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B119,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B119,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B119,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2882,11 +2882,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B120,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B120,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B120,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B120,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2901,11 +2901,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B121,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B121,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B121,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B121,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2920,11 +2920,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B122,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B122,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B122,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B122,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2939,11 +2939,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B123,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B123,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B123,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B123,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2958,11 +2958,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B124,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B124,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B124,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B124,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2977,11 +2977,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B125,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B125,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B125,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B125,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2996,11 +2996,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B126,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B126,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B126,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B126,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3015,11 +3015,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B127,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B127,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B127,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B127,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3034,11 +3034,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B128,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B128,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B128,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B128,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3053,11 +3053,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B129,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B129,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B129,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B129,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3072,11 +3072,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B130,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B130,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B130,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B130,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3091,11 +3091,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B131,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B131,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B131,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B131,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3110,11 +3110,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B132,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B132,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B132,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B132,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3129,11 +3129,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B133,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B133,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B133,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B133,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3148,11 +3148,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B134,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B134,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B134,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B134,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3167,11 +3167,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B135,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B135,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B135,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B135,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3186,11 +3186,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B136,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B136,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B136,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B136,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3205,11 +3205,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B137,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B137,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B137,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B137,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3224,11 +3224,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B138,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B138,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B138,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B138,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3243,11 +3243,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B139,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B139,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B139,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B139,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3262,11 +3262,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B140,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B140,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B140,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B140,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3281,11 +3281,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B141,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B141,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B141,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B141,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3300,11 +3300,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B142,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B142,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B142,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B142,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3319,11 +3319,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B143,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B143,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B143,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B143,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3338,11 +3338,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B144,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B144,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B144,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B144,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3357,11 +3357,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B145,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B145,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B145,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B145,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3376,11 +3376,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B146,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B146,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B146,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B146,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3395,11 +3395,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B147,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B147,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B147,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B147,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3414,11 +3414,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B148,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B148,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B148,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B148,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3433,11 +3433,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B149,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B149,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B149,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B149,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3452,11 +3452,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B150,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B150,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B150,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B150,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3471,11 +3471,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B151,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B151,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B151,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B151,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3490,11 +3490,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B152,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B152,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B152,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B152,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3509,11 +3509,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B153,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B153,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B153,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B153,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3528,11 +3528,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B154,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B154,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B154,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B154,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3547,11 +3547,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B155,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B155,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B155,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B155,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3566,11 +3566,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B156,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B156,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B156,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B156,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3585,11 +3585,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B157,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B157,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B157,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B157,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3604,11 +3604,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B158,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B158,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B158,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B158,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3623,11 +3623,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B159,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B159,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B159,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B159,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3642,11 +3642,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B160,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B160,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B160,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B160,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3661,11 +3661,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B161,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B161,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B161,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B161,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3680,11 +3680,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B162,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B162,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B162,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B162,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3699,11 +3699,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B163,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B163,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B163,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B163,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3718,11 +3718,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B164,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B164,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B164,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B164,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3737,11 +3737,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B165,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B165,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B165,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B165,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3756,11 +3756,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B166,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B166,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B166,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B166,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3775,11 +3775,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B167,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B167,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B167,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B167,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3794,11 +3794,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B168,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B168,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B168,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B168,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3813,11 +3813,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B169,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B169,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B169,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B169,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3832,11 +3832,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B170,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B170,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B170,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B170,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3851,11 +3851,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B171,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B171,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B171,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B171,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3870,11 +3870,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B172,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B172,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B172,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B172,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3889,11 +3889,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B173,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B173,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B173,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B173,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3908,11 +3908,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B174,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B174,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B174,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B174,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3927,11 +3927,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B175,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B175,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B175,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B175,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3946,11 +3946,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B176,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B176,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B176,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B176,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3965,11 +3965,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B177,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B177,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B177,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B177,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3984,11 +3984,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B178,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B178,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B178,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B178,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4003,11 +4003,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B179,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B179,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B179,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B179,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4022,11 +4022,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B180,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B180,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B180,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B180,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4041,11 +4041,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B181,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B181,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B181,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B181,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4060,11 +4060,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B182,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B182,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B182,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B182,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4079,11 +4079,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B183,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B183,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B183,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B183,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4098,11 +4098,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B184,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B184,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B184,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B184,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4117,11 +4117,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B185,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B185,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B185,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B185,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4136,11 +4136,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B186,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B186,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B186,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B186,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4155,11 +4155,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B187,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B187,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B187,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B187,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4174,11 +4174,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B188,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B188,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B188,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B188,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4193,11 +4193,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B189,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B189,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B189,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B189,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4212,11 +4212,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B190,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B190,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B190,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B190,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4231,11 +4231,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B191,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B191,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B191,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B191,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4250,11 +4250,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B192,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B192,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B192,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B192,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4269,11 +4269,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B193,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B193,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B193,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B193,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4288,11 +4288,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B194,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B194,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B194,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B194,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4307,11 +4307,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B195,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B195,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B195,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B195,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4326,11 +4326,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B196,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B196,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B196,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B196,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4345,11 +4345,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B197,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B197,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B197,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B197,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4364,11 +4364,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B198,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B198,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B198,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B198,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4383,11 +4383,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B199,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B199,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B199,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B199,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4402,11 +4402,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B200,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B200,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B200,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B200,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4421,11 +4421,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B201,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B201,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B201,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B201,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4440,11 +4440,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B202,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B202,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B202,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B202,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4459,11 +4459,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B203,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B203,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B203,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B203,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4478,11 +4478,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B204,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B204,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B204,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B204,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4497,11 +4497,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B205,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B205,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B205,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B205,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4516,11 +4516,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B206,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B206,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B206,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B206,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4535,11 +4535,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B207,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B207,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B207,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B207,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4554,11 +4554,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B208,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B208,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B208,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B208,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4573,11 +4573,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B209,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B209,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B209,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B209,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4592,11 +4592,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B210,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B210,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B210,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B210,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4611,11 +4611,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B211,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B211,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B211,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B211,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4630,11 +4630,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B212,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B212,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B212,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B212,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4649,11 +4649,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B213,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B213,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B213,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B213,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4668,11 +4668,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B214,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B214,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B214,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B214,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4687,11 +4687,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B215,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B215,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B215,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B215,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4706,11 +4706,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B216,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B216,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B216,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B216,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4725,11 +4725,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B217,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B217,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B217,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B217,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4744,11 +4744,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B218,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B218,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B218,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B218,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4763,11 +4763,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B219,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B219,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B219,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B219,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4782,11 +4782,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B220,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B220,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B220,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B220,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4801,11 +4801,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B221,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B221,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B221,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B221,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4820,11 +4820,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B222,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B222,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B222,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B222,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4839,11 +4839,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B223,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B223,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B223,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B223,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4858,11 +4858,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B224,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B224,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B224,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B224,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4877,11 +4877,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B225,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B225,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B225,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B225,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4896,11 +4896,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B226,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B226,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B226,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B226,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4915,11 +4915,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B227,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B227,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B227,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B227,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4934,11 +4934,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B228,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B228,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B228,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B228,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4953,11 +4953,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B229,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B229,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B229,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B229,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4972,11 +4972,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B230,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B230,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B230,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B230,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4991,11 +4991,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B231,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B231,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B231,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B231,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5010,11 +5010,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B232,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B232,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B232,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B232,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5029,11 +5029,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B233,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B233,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B233,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B233,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5048,11 +5048,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B234,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B234,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B234,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B234,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5067,11 +5067,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B235,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B235,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B235,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B235,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5086,11 +5086,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B236,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B236,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B236,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B236,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5105,11 +5105,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B237,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B237,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B237,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B237,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5124,11 +5124,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B238,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B238,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B238,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B238,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5143,11 +5143,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B239,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B239,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B239,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B239,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5162,11 +5162,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B240,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B240,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B240,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B240,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5181,11 +5181,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B241,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B241,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B241,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B241,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5200,11 +5200,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B242,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B242,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B242,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B242,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5219,11 +5219,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B243,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B243,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B243,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B243,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5238,11 +5238,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B244,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B244,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B244,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B244,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5257,11 +5257,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B245,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B245,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B245,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B245,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5276,11 +5276,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B246,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B246,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B246,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B246,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5295,11 +5295,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B247,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B247,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B247,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B247,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5314,11 +5314,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B248,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B248,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B248,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B248,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5333,11 +5333,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B249,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B249,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B249,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B249,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5352,11 +5352,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B250,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B250,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B250,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B250,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5371,11 +5371,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B251,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B251,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B251,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B251,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5390,11 +5390,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B252,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B252,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B252,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B252,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5409,11 +5409,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B253,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B253,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B253,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B253,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5428,11 +5428,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B254,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B254,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B254,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B254,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5447,11 +5447,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B255,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B255,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B255,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B255,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5466,11 +5466,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B256,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B256,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B256,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B256,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5485,11 +5485,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B257,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B257,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B257,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B257,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5504,11 +5504,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B258,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B258,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B258,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B258,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5523,11 +5523,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B259,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B259,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B259,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B259,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5542,11 +5542,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B260,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B260,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B260,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B260,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5561,11 +5561,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B261,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B261,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B261,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B261,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5580,11 +5580,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B262,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B262,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B262,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B262,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5599,11 +5599,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B263,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B263,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B263,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B263,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5618,11 +5618,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B264,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B264,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B264,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B264,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5637,11 +5637,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B265,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B265,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B265,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B265,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5656,11 +5656,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B266,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B266,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B266,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B266,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5675,11 +5675,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B267,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B267,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B267,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B267,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5694,11 +5694,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B268,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B268,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B268,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B268,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5713,11 +5713,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B269,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B269,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B269,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B269,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5732,11 +5732,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B270,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B270,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B270,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B270,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5751,11 +5751,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B271,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B271,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B271,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B271,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5770,11 +5770,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B272,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B272,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B272,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B272,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5789,11 +5789,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B273,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B273,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B273,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B273,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5808,11 +5808,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B274,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B274,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B274,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B274,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5827,11 +5827,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B275,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B275,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B275,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B275,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5846,11 +5846,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B276,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B276,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B276,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B276,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5865,11 +5865,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B277,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B277,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B277,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B277,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5884,11 +5884,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B278,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B278,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B278,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B278,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5903,11 +5903,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B279,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B279,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B279,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B279,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5922,11 +5922,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B280,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B280,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B280,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B280,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5941,11 +5941,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B281,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B281,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B281,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B281,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5960,11 +5960,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B282,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B282,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B282,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B282,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5979,11 +5979,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B283,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B283,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B283,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B283,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5998,11 +5998,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B284,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B284,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B284,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B284,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6017,11 +6017,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B285,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B285,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B285,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B285,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6036,11 +6036,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B286,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B286,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B286,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B286,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6055,11 +6055,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B287,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B287,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B287,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B287,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6074,11 +6074,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B288,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B288,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B288,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B288,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6093,11 +6093,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B289,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B289,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B289,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B289,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6112,11 +6112,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B290,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B290,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B290,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B290,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6131,11 +6131,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B291,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B291,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B291,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B291,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6150,11 +6150,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B292,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B292,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B292,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B292,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6169,11 +6169,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B293,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B293,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B293,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B293,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6188,11 +6188,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B294,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B294,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B294,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B294,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6207,11 +6207,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B295,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B295,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B295,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B295,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6226,11 +6226,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B296,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B296,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B296,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B296,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6245,11 +6245,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B297,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B297,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B297,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B297,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6264,11 +6264,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B298,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B298,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B298,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B298,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6283,11 +6283,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B299,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B299,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B299,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B299,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6302,11 +6302,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B300,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B300,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B300,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B300,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6321,11 +6321,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B301,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B301,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B301,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B301,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6340,11 +6340,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B302,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B302,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B302,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B302,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6359,11 +6359,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B303,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B303,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B303,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B303,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6378,11 +6378,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B304,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B304,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B304,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B304,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6397,11 +6397,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B305,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B305,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B305,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B305,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6416,11 +6416,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B306,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B306,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B306,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B306,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6435,11 +6435,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B307,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B307,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B307,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B307,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6454,11 +6454,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B308,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B308,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B308,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B308,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6473,11 +6473,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B309,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B309,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B309,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B309,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6492,11 +6492,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B310,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B310,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B310,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B310,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6511,11 +6511,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B311,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B311,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B311,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B311,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6530,11 +6530,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B312,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B312,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B312,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B312,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6549,11 +6549,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B313,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B313,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B313,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B313,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6568,11 +6568,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B314,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B314,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B314,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B314,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6587,11 +6587,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B315,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B315,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B315,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B315,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6606,11 +6606,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B316,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B316,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B316,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B316,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6625,11 +6625,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B317,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B317,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B317,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B317,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6644,11 +6644,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B318,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B318,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B318,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B318,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6663,11 +6663,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B319,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B319,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B319,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B319,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6682,11 +6682,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B320,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B320,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B320,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B320,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6701,11 +6701,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B321,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B321,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B321,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B321,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6720,11 +6720,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B322,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B322,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B322,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B322,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6739,11 +6739,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B323,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B323,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B323,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B323,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6758,11 +6758,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B324,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B324,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B324,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B324,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6777,11 +6777,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B325,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B325,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B325,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B325,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6796,11 +6796,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B326,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B326,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B326,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B326,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6815,11 +6815,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B327,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B327,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B327,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B327,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6834,11 +6834,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B328,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B328,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B328,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B328,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6853,11 +6853,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B329,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B329,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B329,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B329,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6872,11 +6872,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B330,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B330,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B330,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B330,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6891,11 +6891,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B331,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B331,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B331,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B331,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6910,11 +6910,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B332,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B332,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B332,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B332,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6929,11 +6929,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B333,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B333,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B333,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B333,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6948,11 +6948,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B334,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B334,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B334,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B334,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6967,11 +6967,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B335,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B335,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B335,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B335,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6986,11 +6986,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B336,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B336,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B336,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B336,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7005,11 +7005,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B337,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B337,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B337,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B337,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7024,11 +7024,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B338,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B338,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B338,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B338,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7043,11 +7043,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B339,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B339,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B339,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B339,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7062,11 +7062,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B340,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B340,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B340,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B340,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7081,11 +7081,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B341,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B341,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B341,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B341,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7100,11 +7100,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B342,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B342,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B342,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B342,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7119,11 +7119,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B343,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B343,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B343,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B343,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7138,11 +7138,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B344,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B344,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B344,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B344,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7157,11 +7157,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B345,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B345,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B345,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B345,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7176,11 +7176,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B346,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B346,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B346,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B346,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7195,11 +7195,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B347,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B347,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B347,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B347,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7214,11 +7214,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B348,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B348,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B348,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B348,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7233,11 +7233,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B349,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B349,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B349,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B349,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7252,11 +7252,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B350,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B350,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B350,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B350,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7271,11 +7271,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B351,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B351,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B351,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B351,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7290,11 +7290,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B352,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B352,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B352,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B352,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7309,11 +7309,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B353,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B353,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B353,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B353,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7328,11 +7328,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B354,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B354,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B354,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B354,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7347,11 +7347,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B355,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B355,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B355,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B355,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7366,11 +7366,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B356,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B356,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B356,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B356,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7385,11 +7385,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B357,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B357,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B357,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B357,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7404,11 +7404,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B358,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B358,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B358,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B358,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7423,11 +7423,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B359,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B359,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B359,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B359,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7442,11 +7442,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B360,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B360,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B360,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B360,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7461,11 +7461,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B361,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B361,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B361,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B361,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7480,11 +7480,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B362,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B362,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B362,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B362,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7499,11 +7499,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B363,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B363,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B363,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B363,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7518,11 +7518,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B364,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B364,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B364,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B364,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7537,11 +7537,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B365,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B365,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B365,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B365,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7556,11 +7556,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B366,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B366,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B366,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B366,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7575,11 +7575,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B367,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B367,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B367,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B367,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7594,11 +7594,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B368,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B368,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B368,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B368,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7613,11 +7613,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B369,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B369,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B369,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B369,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7632,11 +7632,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B370,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B370,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B370,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B370,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7651,11 +7651,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B371,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B371,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B371,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B371,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7670,11 +7670,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B372,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B372,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B372,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B372,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7689,11 +7689,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B373,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B373,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B373,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B373,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7708,11 +7708,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B374,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B374,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B374,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B374,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7727,11 +7727,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B375,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B375,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B375,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B375,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7746,11 +7746,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B376,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B376,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B376,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B376,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7765,11 +7765,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B377,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B377,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B377,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B377,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7784,11 +7784,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B378,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B378,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B378,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B378,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7803,11 +7803,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B379,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B379,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B379,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B379,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7822,11 +7822,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B380,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B380,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B380,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B380,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7841,11 +7841,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B381,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B381,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B381,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B381,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7860,11 +7860,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B382,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B382,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B382,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B382,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7879,11 +7879,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B383,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B383,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B383,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B383,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7898,11 +7898,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B384,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B384,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B384,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B384,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7917,11 +7917,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B385,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B385,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B385,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B385,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7936,11 +7936,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B386,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B386,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B386,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B386,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7955,11 +7955,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B387,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B387,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B387,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B387,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7974,11 +7974,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B388,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B388,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B388,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B388,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7993,11 +7993,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B389,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B389,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B389,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B389,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8012,11 +8012,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B390,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B390,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B390,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B390,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8031,11 +8031,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B391,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B391,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B391,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B391,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8050,11 +8050,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B392,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B392,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B392,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B392,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8069,11 +8069,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B393,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B393,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B393,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B393,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8088,11 +8088,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B394,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B394,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B394,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B394,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8107,11 +8107,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B395,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B395,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B395,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B395,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8126,11 +8126,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B396,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B396,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B396,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B396,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8145,11 +8145,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B397,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B397,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B397,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B397,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8164,11 +8164,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B398,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B398,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B398,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B398,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8183,11 +8183,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B399,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B399,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B399,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B399,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8202,11 +8202,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B400,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B400,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B400,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B400,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8221,11 +8221,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B401,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B401,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B401,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B401,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8240,11 +8240,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$179,MATCH(B402,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B402,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$179,MATCH(B402,Productos!$A$2:$A$179,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B402,Productos!$A$2:$A$178,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9555,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
     </row>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
     </row>
@@ -9595,11 +9595,6 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11121,7 +11116,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11381,7 +11376,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11481,7 +11476,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11681,7 +11676,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11801,7 +11796,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12332,16 +12327,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>90401421000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12352,16 +12347,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>90401421000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12372,16 +12367,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12392,16 +12387,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12412,16 +12407,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12432,16 +12427,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12452,16 +12447,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12472,16 +12467,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12492,16 +12487,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12512,16 +12507,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12532,16 +12527,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12552,16 +12547,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12572,16 +12567,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12592,16 +12587,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93519520000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12612,16 +12607,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>93519520000</t>
+          <t>93519480000</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12632,16 +12627,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>93519480000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12652,16 +12647,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90038410000</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12672,16 +12667,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>90038410000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12692,16 +12687,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12712,16 +12707,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>90038400000</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12732,16 +12727,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>90038400000</t>
+          <t>90038390000</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12752,16 +12747,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>90038390000</t>
+          <t>93519990000</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12772,16 +12767,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>93519990000</t>
+          <t>90038570000</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12792,16 +12787,16 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>90038570000</t>
+          <t>93519970000</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12812,12 +12807,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
+          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>93519970000</t>
+          <t>90401980000</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -12825,19 +12820,19 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
+          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>90401980000</t>
+          <t>90401430000</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -12852,16 +12847,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
+          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>90401430000</t>
+          <t>90412110000</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12872,16 +12867,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>90412110000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12892,12 +12887,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>90006770000</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -12912,16 +12907,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>90006770000</t>
+          <t>93505710000</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12932,16 +12927,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>93505710000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12952,16 +12947,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12972,16 +12967,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12992,16 +12987,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13012,16 +13007,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>90404120000</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13032,16 +13027,16 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>90404120000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13052,16 +13047,16 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>90407030000</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13072,12 +13067,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>90407030000</t>
+          <t>90414301000</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -13092,52 +13087,52 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>90414301000</t>
+          <t>93511630000</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>D SHED-X SUPLEMENTO NUTRI /PERROS 8 · 90329810000</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>93511630000</t>
+          <t>90329810000</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>D SHED-X SUPLEMENTO NUTRI /PERROS 8 · 90329810000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>90329810000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -13145,19 +13140,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90410980000</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -13172,12 +13167,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
+          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>90410980000</t>
+          <t>935096300001</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -13185,23 +13180,23 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
+          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>935096300001</t>
+          <t>93501390000</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13212,36 +13207,36 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
+          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>93501390000</t>
+          <t>93514810000</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
+          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>93514810000</t>
+          <t>93517660000</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13249,57 +13244,37 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>93517660000</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>P&amp;G | HOSPITAL PARQUE LEFEVRE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>P&amp;G | HOSPITAL PARQUE LEFEVRE</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>19.10.2026</t>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/106.xlsx
+++ b/plantillas/106.xlsx
@@ -28,11 +28,11 @@
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$4</definedName>
     <definedName name="MARCA_16">Listas!$S$2:$S$19</definedName>
-    <definedName name="MARCA_17">Listas!$T$2:$T$37</definedName>
+    <definedName name="MARCA_17">Listas!$T$2:$T$36</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$3</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$9</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$26</definedName>
-    <definedName name="MARCA_21">Listas!$X$2:$X$15</definedName>
+    <definedName name="MARCA_21">Listas!$X$2:$X$14</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$2</definedName>
     <definedName name="MARCA_23">Listas!$Z$2:$Z$2</definedName>
     <definedName name="MARCA_24">Listas!$AA$2:$AA$3</definedName>
@@ -644,11 +644,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B3,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B3,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B3,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B3,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -668,11 +668,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B4,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B4,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B4,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B4,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -692,11 +692,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B5,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B5,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B5,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B5,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -716,11 +716,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B6,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B6,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B6,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B6,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -735,11 +735,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B7,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B7,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B7,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B7,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -754,11 +754,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B8,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B8,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B8,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B8,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -773,11 +773,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B9,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B9,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B9,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B9,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -792,11 +792,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B10,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B10,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B10,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B10,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -811,11 +811,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B11,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B11,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B11,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B11,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -830,11 +830,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B12,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B12,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B12,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B12,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -849,11 +849,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B13,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B13,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B13,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B13,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -868,11 +868,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B14,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B14,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B14,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B14,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -887,11 +887,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B15,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B15,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B15,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B15,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -906,11 +906,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B16,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B16,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B16,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B16,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -925,11 +925,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B17,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B17,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B17,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B17,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -944,11 +944,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B18,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B18,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B18,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B18,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -963,11 +963,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B19,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B19,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B19,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B19,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -982,11 +982,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B20,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B20,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B20,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B20,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1001,11 +1001,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B21,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B21,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B21,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B21,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1020,11 +1020,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B22,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B22,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B22,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B22,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1039,11 +1039,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B23,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B23,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B23,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B23,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1058,11 +1058,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B24,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B24,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B24,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B24,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1077,11 +1077,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B25,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B25,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B25,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B25,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1096,11 +1096,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B26,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B26,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B26,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B26,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1115,11 +1115,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B27,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B27,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B27,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B27,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1134,11 +1134,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B28,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B28,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B28,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B28,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1153,11 +1153,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B29,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B29,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B29,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B29,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1172,11 +1172,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B30,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B30,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B30,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B30,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1191,11 +1191,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B31,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B31,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B31,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B31,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1210,11 +1210,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B32,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B32,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B32,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B32,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1229,11 +1229,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B33,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B33,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B33,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B33,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1248,11 +1248,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B34,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B34,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B34,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B34,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1267,11 +1267,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B35,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B35,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B35,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B35,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1286,11 +1286,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B36,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B36,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B36,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B36,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1305,11 +1305,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B37,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B37,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B37,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B37,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1324,11 +1324,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B38,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B38,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B38,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B38,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1343,11 +1343,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B39,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B39,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B39,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B39,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1362,11 +1362,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B40,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B40,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B40,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B40,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1381,11 +1381,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B41,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B41,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B41,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B41,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1400,11 +1400,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B42,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B42,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B42,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B42,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1419,11 +1419,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B43,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B43,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B43,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B43,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1438,11 +1438,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B44,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B44,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B44,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B44,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1457,11 +1457,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B45,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B45,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B45,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B45,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1476,11 +1476,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B46,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B46,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B46,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B46,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1495,11 +1495,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B47,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B47,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B47,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B47,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1514,11 +1514,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B48,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B48,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B48,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B48,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1533,11 +1533,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B49,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B49,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B49,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B49,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1552,11 +1552,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B50,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B50,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B50,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B50,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1571,11 +1571,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B51,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B51,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B51,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B51,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1590,11 +1590,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B52,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B52,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B52,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B52,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1609,11 +1609,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B53,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B53,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B53,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B53,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1628,11 +1628,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B54,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B54,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B54,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B54,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1647,11 +1647,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B55,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B55,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B55,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B55,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1666,11 +1666,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B56,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B56,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B56,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B56,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1685,11 +1685,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B57,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B57,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B57,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B57,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1704,11 +1704,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B58,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B58,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B58,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B58,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1723,11 +1723,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B59,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B59,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B59,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B59,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1742,11 +1742,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B60,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B60,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B60,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B60,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1761,11 +1761,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B61,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B61,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B61,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B61,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1780,11 +1780,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B62,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B62,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B62,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B62,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1799,11 +1799,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B63,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B63,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B63,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B63,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1818,11 +1818,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B64,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B64,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B64,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B64,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1837,11 +1837,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B65,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B65,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B65,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B65,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1856,11 +1856,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B66,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B66,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B66,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B66,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1875,11 +1875,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B67,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B67,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B67,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B67,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1894,11 +1894,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B68,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B68,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B68,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B68,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1913,11 +1913,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B69,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B69,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B69,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B69,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1932,11 +1932,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B70,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B70,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B70,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B70,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1951,11 +1951,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B71,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B71,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B71,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B71,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1970,11 +1970,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B72,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B72,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B72,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B72,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1989,11 +1989,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B73,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B73,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B73,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B73,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2008,11 +2008,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B74,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B74,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B74,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B74,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2027,11 +2027,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B75,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B75,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B75,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B75,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2046,11 +2046,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B76,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B76,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B76,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B76,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2065,11 +2065,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B77,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B77,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B77,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B77,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2084,11 +2084,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B78,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B78,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B78,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B78,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2103,11 +2103,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B79,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B79,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B79,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B79,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2122,11 +2122,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B80,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B80,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B80,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B80,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2141,11 +2141,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B81,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B81,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B81,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B81,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2160,11 +2160,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B82,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B82,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B82,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B82,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2179,11 +2179,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B83,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B83,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B83,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B83,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2198,11 +2198,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B84,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B84,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B84,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B84,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2217,11 +2217,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B85,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B85,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B85,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B85,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2236,11 +2236,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B86,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B86,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B86,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B86,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2255,11 +2255,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B87,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B87,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B87,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B87,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2274,11 +2274,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B88,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B88,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B88,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B88,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2293,11 +2293,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B89,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B89,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B89,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B89,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2312,11 +2312,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B90,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B90,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B90,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B90,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2331,11 +2331,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B91,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B91,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B91,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B91,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2350,11 +2350,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B92,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B92,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B92,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B92,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2369,11 +2369,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B93,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B93,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B93,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B93,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2388,11 +2388,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B94,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B94,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B94,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B94,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2407,11 +2407,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B95,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B95,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B95,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B95,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2426,11 +2426,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B96,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B96,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B96,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B96,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2445,11 +2445,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B97,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B97,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B97,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B97,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2464,11 +2464,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B98,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B98,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B98,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B98,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2483,11 +2483,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B99,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B99,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B99,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B99,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2502,11 +2502,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B100,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B100,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B100,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B100,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2521,11 +2521,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B101,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B101,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B101,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B101,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2540,11 +2540,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B102,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B102,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B102,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B102,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2559,11 +2559,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B103,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B103,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B103,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B103,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2578,11 +2578,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B104,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B104,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B104,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B104,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2597,11 +2597,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B105,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B105,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B105,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B105,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2616,11 +2616,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B106,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B106,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B106,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B106,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2635,11 +2635,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B107,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B107,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B107,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B107,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2654,11 +2654,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B108,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B108,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B108,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B108,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2673,11 +2673,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B109,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B109,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B109,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B109,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2692,11 +2692,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B110,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B110,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B110,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B110,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2711,11 +2711,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B111,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B111,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B111,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B111,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2730,11 +2730,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B112,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B112,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B112,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B112,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2749,11 +2749,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B113,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B113,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B113,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B113,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2768,11 +2768,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B114,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B114,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B114,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B114,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2787,11 +2787,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B115,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B115,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B115,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B115,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2806,11 +2806,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B116,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B116,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B116,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B116,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2825,11 +2825,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B117,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B117,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B117,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B117,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2844,11 +2844,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B118,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B118,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B118,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B118,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2863,11 +2863,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B119,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B119,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B119,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B119,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2882,11 +2882,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B120,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B120,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B120,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B120,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2901,11 +2901,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B121,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B121,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B121,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B121,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2920,11 +2920,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B122,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B122,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B122,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B122,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2939,11 +2939,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B123,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B123,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B123,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B123,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2958,11 +2958,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B124,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B124,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B124,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B124,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2977,11 +2977,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B125,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B125,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B125,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B125,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2996,11 +2996,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B126,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B126,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B126,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B126,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3015,11 +3015,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B127,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B127,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B127,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B127,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3034,11 +3034,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B128,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B128,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B128,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B128,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3053,11 +3053,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B129,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B129,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B129,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B129,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3072,11 +3072,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B130,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B130,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B130,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B130,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3091,11 +3091,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B131,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B131,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B131,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B131,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3110,11 +3110,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B132,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B132,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B132,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B132,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3129,11 +3129,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B133,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B133,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B133,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B133,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3148,11 +3148,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B134,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B134,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B134,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B134,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3167,11 +3167,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B135,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B135,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B135,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B135,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3186,11 +3186,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B136,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B136,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B136,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B136,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3205,11 +3205,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B137,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B137,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B137,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B137,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3224,11 +3224,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B138,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B138,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B138,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B138,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3243,11 +3243,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B139,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B139,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B139,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B139,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3262,11 +3262,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B140,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B140,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B140,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B140,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3281,11 +3281,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B141,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B141,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B141,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B141,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3300,11 +3300,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B142,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B142,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B142,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B142,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3319,11 +3319,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B143,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B143,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B143,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B143,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3338,11 +3338,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B144,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B144,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B144,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B144,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3357,11 +3357,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B145,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B145,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B145,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B145,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3376,11 +3376,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B146,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B146,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B146,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B146,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3395,11 +3395,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B147,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B147,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B147,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B147,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3414,11 +3414,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B148,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B148,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B148,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B148,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3433,11 +3433,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B149,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B149,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B149,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B149,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3452,11 +3452,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B150,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B150,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B150,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B150,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3471,11 +3471,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B151,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B151,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B151,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B151,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3490,11 +3490,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B152,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B152,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B152,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B152,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3509,11 +3509,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B153,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B153,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B153,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B153,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3528,11 +3528,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B154,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B154,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B154,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B154,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3547,11 +3547,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B155,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B155,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B155,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B155,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3566,11 +3566,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B156,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B156,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B156,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B156,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3585,11 +3585,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B157,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B157,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B157,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B157,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3604,11 +3604,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B158,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B158,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B158,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B158,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3623,11 +3623,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B159,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B159,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B159,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B159,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3642,11 +3642,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B160,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B160,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B160,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B160,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3661,11 +3661,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B161,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B161,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B161,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B161,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3680,11 +3680,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B162,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B162,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B162,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B162,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3699,11 +3699,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B163,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B163,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B163,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B163,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3718,11 +3718,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B164,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B164,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B164,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B164,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3737,11 +3737,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B165,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B165,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B165,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B165,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3756,11 +3756,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B166,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B166,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B166,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B166,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3775,11 +3775,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B167,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B167,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B167,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B167,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3794,11 +3794,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B168,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B168,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B168,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B168,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3813,11 +3813,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B169,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B169,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B169,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B169,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3832,11 +3832,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B170,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B170,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B170,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B170,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3851,11 +3851,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B171,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B171,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B171,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B171,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3870,11 +3870,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B172,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B172,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B172,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B172,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3889,11 +3889,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B173,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B173,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B173,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B173,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3908,11 +3908,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B174,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B174,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B174,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B174,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3927,11 +3927,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B175,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B175,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B175,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B175,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3946,11 +3946,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B176,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B176,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B176,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B176,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3965,11 +3965,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B177,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B177,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B177,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B177,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3984,11 +3984,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B178,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B178,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B178,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B178,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4003,11 +4003,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B179,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B179,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B179,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B179,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4022,11 +4022,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B180,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B180,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B180,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B180,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4041,11 +4041,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B181,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B181,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B181,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B181,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4060,11 +4060,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B182,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B182,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B182,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B182,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4079,11 +4079,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B183,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B183,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B183,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B183,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4098,11 +4098,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B184,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B184,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B184,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B184,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4117,11 +4117,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B185,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B185,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B185,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B185,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4136,11 +4136,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B186,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B186,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B186,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B186,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4155,11 +4155,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B187,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B187,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B187,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B187,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4174,11 +4174,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B188,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B188,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B188,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B188,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4193,11 +4193,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B189,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B189,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B189,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B189,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4212,11 +4212,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B190,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B190,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B190,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B190,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4231,11 +4231,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B191,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B191,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B191,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B191,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4250,11 +4250,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B192,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B192,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B192,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B192,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4269,11 +4269,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B193,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B193,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B193,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B193,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4288,11 +4288,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B194,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B194,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B194,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B194,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4307,11 +4307,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B195,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B195,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B195,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B195,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4326,11 +4326,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B196,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B196,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B196,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B196,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4345,11 +4345,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B197,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B197,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B197,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B197,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4364,11 +4364,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B198,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B198,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B198,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B198,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4383,11 +4383,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B199,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B199,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B199,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B199,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4402,11 +4402,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B200,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B200,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B200,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B200,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4421,11 +4421,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B201,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B201,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B201,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B201,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4440,11 +4440,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B202,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B202,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B202,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B202,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4459,11 +4459,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B203,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B203,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B203,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B203,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4478,11 +4478,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B204,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B204,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B204,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B204,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4497,11 +4497,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B205,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B205,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B205,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B205,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4516,11 +4516,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B206,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B206,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B206,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B206,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4535,11 +4535,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B207,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B207,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B207,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B207,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4554,11 +4554,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B208,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B208,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B208,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B208,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4573,11 +4573,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B209,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B209,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B209,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B209,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4592,11 +4592,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B210,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B210,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B210,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B210,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4611,11 +4611,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B211,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B211,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B211,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B211,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4630,11 +4630,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B212,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B212,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B212,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B212,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4649,11 +4649,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B213,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B213,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B213,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B213,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4668,11 +4668,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B214,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B214,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B214,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B214,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4687,11 +4687,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B215,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B215,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B215,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B215,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4706,11 +4706,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B216,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B216,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B216,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B216,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4725,11 +4725,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B217,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B217,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B217,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B217,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4744,11 +4744,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B218,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B218,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B218,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B218,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4763,11 +4763,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B219,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B219,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B219,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B219,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4782,11 +4782,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B220,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B220,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B220,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B220,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4801,11 +4801,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B221,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B221,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B221,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B221,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4820,11 +4820,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B222,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B222,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B222,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B222,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4839,11 +4839,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B223,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B223,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B223,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B223,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4858,11 +4858,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B224,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B224,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B224,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B224,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4877,11 +4877,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B225,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B225,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B225,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B225,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4896,11 +4896,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B226,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B226,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B226,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B226,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4915,11 +4915,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B227,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B227,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B227,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B227,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4934,11 +4934,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B228,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B228,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B228,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B228,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4953,11 +4953,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B229,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B229,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B229,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B229,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4972,11 +4972,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B230,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B230,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B230,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B230,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4991,11 +4991,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B231,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B231,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B231,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B231,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5010,11 +5010,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B232,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B232,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B232,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B232,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5029,11 +5029,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B233,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B233,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B233,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B233,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5048,11 +5048,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B234,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B234,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B234,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B234,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5067,11 +5067,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B235,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B235,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B235,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B235,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5086,11 +5086,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B236,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B236,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B236,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B236,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5105,11 +5105,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B237,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B237,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B237,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B237,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5124,11 +5124,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B238,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B238,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B238,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B238,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5143,11 +5143,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B239,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B239,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B239,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B239,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5162,11 +5162,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B240,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B240,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B240,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B240,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5181,11 +5181,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B241,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B241,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B241,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B241,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5200,11 +5200,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B242,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B242,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B242,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B242,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5219,11 +5219,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B243,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B243,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B243,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B243,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5238,11 +5238,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B244,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B244,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B244,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B244,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5257,11 +5257,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B245,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B245,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B245,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B245,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5276,11 +5276,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B246,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B246,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B246,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B246,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5295,11 +5295,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B247,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B247,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B247,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B247,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5314,11 +5314,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B248,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B248,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B248,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B248,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5333,11 +5333,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B249,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B249,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B249,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B249,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5352,11 +5352,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B250,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B250,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B250,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B250,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5371,11 +5371,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B251,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B251,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B251,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B251,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5390,11 +5390,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B252,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B252,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B252,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B252,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5409,11 +5409,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B253,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B253,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B253,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B253,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5428,11 +5428,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B254,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B254,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B254,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B254,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5447,11 +5447,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B255,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B255,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B255,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B255,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5466,11 +5466,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B256,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B256,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B256,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B256,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5485,11 +5485,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B257,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B257,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B257,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B257,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5504,11 +5504,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B258,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B258,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B258,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B258,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5523,11 +5523,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B259,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B259,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B259,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B259,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5542,11 +5542,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B260,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B260,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B260,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B260,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5561,11 +5561,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B261,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B261,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B261,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B261,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5580,11 +5580,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B262,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B262,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B262,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B262,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5599,11 +5599,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B263,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B263,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B263,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B263,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5618,11 +5618,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B264,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B264,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B264,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B264,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5637,11 +5637,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B265,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B265,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B265,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B265,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5656,11 +5656,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B266,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B266,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B266,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B266,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5675,11 +5675,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B267,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B267,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B267,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B267,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5694,11 +5694,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B268,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B268,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B268,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B268,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5713,11 +5713,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B269,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B269,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B269,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B269,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5732,11 +5732,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B270,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B270,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B270,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B270,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5751,11 +5751,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B271,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B271,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B271,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B271,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5770,11 +5770,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B272,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B272,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B272,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B272,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5789,11 +5789,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B273,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B273,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B273,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B273,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5808,11 +5808,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B274,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B274,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B274,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B274,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5827,11 +5827,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B275,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B275,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B275,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B275,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5846,11 +5846,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B276,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B276,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B276,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B276,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5865,11 +5865,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B277,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B277,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B277,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B277,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5884,11 +5884,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B278,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B278,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B278,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B278,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5903,11 +5903,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B279,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B279,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B279,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B279,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5922,11 +5922,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B280,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B280,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B280,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B280,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5941,11 +5941,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B281,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B281,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B281,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B281,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5960,11 +5960,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B282,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B282,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B282,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B282,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5979,11 +5979,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B283,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B283,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B283,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B283,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5998,11 +5998,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B284,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B284,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B284,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B284,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6017,11 +6017,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B285,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B285,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B285,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B285,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6036,11 +6036,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B286,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B286,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B286,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B286,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6055,11 +6055,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B287,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B287,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B287,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B287,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6074,11 +6074,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B288,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B288,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B288,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B288,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6093,11 +6093,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B289,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B289,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B289,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B289,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6112,11 +6112,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B290,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B290,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B290,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B290,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6131,11 +6131,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B291,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B291,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B291,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B291,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6150,11 +6150,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B292,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B292,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B292,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B292,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6169,11 +6169,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B293,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B293,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B293,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B293,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6188,11 +6188,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B294,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B294,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B294,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B294,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6207,11 +6207,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B295,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B295,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B295,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B295,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6226,11 +6226,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B296,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B296,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B296,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B296,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6245,11 +6245,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B297,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B297,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B297,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B297,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6264,11 +6264,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B298,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B298,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B298,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B298,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6283,11 +6283,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B299,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B299,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B299,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B299,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6302,11 +6302,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B300,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B300,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B300,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B300,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6321,11 +6321,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B301,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B301,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B301,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B301,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6340,11 +6340,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B302,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B302,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B302,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B302,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6359,11 +6359,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B303,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B303,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B303,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B303,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6378,11 +6378,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B304,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B304,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B304,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B304,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6397,11 +6397,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B305,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B305,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B305,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B305,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6416,11 +6416,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B306,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B306,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B306,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B306,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6435,11 +6435,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B307,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B307,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B307,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B307,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6454,11 +6454,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B308,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B308,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B308,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B308,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6473,11 +6473,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B309,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B309,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B309,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B309,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6492,11 +6492,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B310,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B310,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B310,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B310,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6511,11 +6511,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B311,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B311,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B311,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B311,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6530,11 +6530,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B312,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B312,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B312,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B312,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6549,11 +6549,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B313,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B313,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B313,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B313,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6568,11 +6568,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B314,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B314,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B314,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B314,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6587,11 +6587,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B315,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B315,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B315,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B315,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6606,11 +6606,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B316,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B316,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B316,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B316,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6625,11 +6625,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B317,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B317,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B317,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B317,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6644,11 +6644,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B318,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B318,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B318,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B318,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6663,11 +6663,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B319,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B319,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B319,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B319,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6682,11 +6682,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B320,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B320,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B320,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B320,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6701,11 +6701,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B321,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B321,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B321,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B321,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6720,11 +6720,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B322,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B322,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B322,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B322,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6739,11 +6739,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B323,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B323,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B323,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B323,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6758,11 +6758,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B324,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B324,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B324,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B324,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6777,11 +6777,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B325,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B325,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B325,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B325,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6796,11 +6796,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B326,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B326,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B326,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B326,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6815,11 +6815,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B327,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B327,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B327,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B327,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6834,11 +6834,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B328,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B328,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B328,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B328,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6853,11 +6853,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B329,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B329,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B329,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B329,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6872,11 +6872,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B330,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B330,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B330,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B330,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6891,11 +6891,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B331,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B331,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B331,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B331,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6910,11 +6910,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B332,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B332,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B332,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B332,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6929,11 +6929,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B333,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B333,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B333,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B333,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6948,11 +6948,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B334,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B334,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B334,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B334,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6967,11 +6967,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B335,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B335,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B335,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B335,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6986,11 +6986,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B336,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B336,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B336,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B336,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7005,11 +7005,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B337,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B337,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B337,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B337,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7024,11 +7024,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B338,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B338,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B338,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B338,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7043,11 +7043,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B339,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B339,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B339,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B339,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7062,11 +7062,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B340,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B340,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B340,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B340,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7081,11 +7081,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B341,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B341,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B341,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B341,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7100,11 +7100,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B342,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B342,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B342,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B342,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7119,11 +7119,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B343,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B343,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B343,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B343,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7138,11 +7138,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B344,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B344,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B344,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B344,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7157,11 +7157,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B345,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B345,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B345,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B345,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7176,11 +7176,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B346,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B346,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B346,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B346,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7195,11 +7195,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B347,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B347,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B347,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B347,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7214,11 +7214,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B348,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B348,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B348,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B348,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7233,11 +7233,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B349,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B349,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B349,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B349,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7252,11 +7252,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B350,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B350,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B350,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B350,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7271,11 +7271,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B351,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B351,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B351,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B351,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7290,11 +7290,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B352,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B352,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B352,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B352,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7309,11 +7309,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B353,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B353,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B353,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B353,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7328,11 +7328,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B354,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B354,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B354,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B354,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7347,11 +7347,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B355,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B355,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B355,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B355,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7366,11 +7366,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B356,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B356,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B356,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B356,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7385,11 +7385,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B357,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B357,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B357,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B357,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7404,11 +7404,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B358,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B358,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B358,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B358,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7423,11 +7423,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B359,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B359,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B359,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B359,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7442,11 +7442,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B360,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B360,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B360,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B360,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7461,11 +7461,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B361,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B361,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B361,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B361,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7480,11 +7480,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B362,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B362,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B362,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B362,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7499,11 +7499,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B363,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B363,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B363,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B363,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7518,11 +7518,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B364,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B364,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B364,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B364,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7537,11 +7537,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B365,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B365,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B365,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B365,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7556,11 +7556,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B366,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B366,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B366,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B366,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7575,11 +7575,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B367,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B367,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B367,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B367,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7594,11 +7594,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B368,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B368,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B368,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B368,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7613,11 +7613,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B369,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B369,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B369,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B369,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7632,11 +7632,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B370,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B370,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B370,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B370,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7651,11 +7651,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B371,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B371,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B371,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B371,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7670,11 +7670,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B372,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B372,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B372,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B372,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7689,11 +7689,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B373,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B373,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B373,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B373,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7708,11 +7708,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B374,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B374,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B374,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B374,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7727,11 +7727,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B375,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B375,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B375,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B375,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7746,11 +7746,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B376,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B376,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B376,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B376,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7765,11 +7765,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B377,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B377,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B377,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B377,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7784,11 +7784,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B378,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B378,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B378,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B378,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7803,11 +7803,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B379,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B379,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B379,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B379,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7822,11 +7822,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B380,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B380,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B380,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B380,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7841,11 +7841,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B381,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B381,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B381,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B381,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7860,11 +7860,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B382,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B382,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B382,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B382,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7879,11 +7879,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B383,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B383,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B383,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B383,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7898,11 +7898,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B384,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B384,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B384,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B384,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7917,11 +7917,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B385,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B385,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B385,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B385,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7936,11 +7936,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B386,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B386,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B386,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B386,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7955,11 +7955,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B387,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B387,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B387,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B387,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7974,11 +7974,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B388,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B388,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B388,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B388,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7993,11 +7993,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B389,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B389,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B389,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B389,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8012,11 +8012,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B390,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B390,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B390,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B390,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8031,11 +8031,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B391,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B391,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B391,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B391,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8050,11 +8050,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B392,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B392,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B392,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B392,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8069,11 +8069,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B393,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B393,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B393,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B393,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8088,11 +8088,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B394,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B394,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B394,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B394,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8107,11 +8107,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B395,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B395,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B395,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B395,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8126,11 +8126,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B396,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B396,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B396,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B396,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8145,11 +8145,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B397,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B397,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B397,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B397,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8164,11 +8164,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B398,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B398,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B398,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B398,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8183,11 +8183,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B399,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B399,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B399,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B399,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8202,11 +8202,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B400,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B400,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B400,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B400,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8221,11 +8221,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B401,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B401,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B401,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B401,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8240,11 +8240,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$178,MATCH(B402,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$176,MATCH(B402,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$178,MATCH(B402,Productos!$A$2:$A$178,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$176,MATCH(B402,Productos!$A$2:$A$176,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8285,7 +8285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
+          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
     </row>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
     </row>
@@ -9255,17 +9255,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9287,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -9324,7 +9319,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -9356,7 +9351,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -9388,7 +9383,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
+          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -9415,7 +9410,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -9442,7 +9437,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -9469,7 +9464,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -9496,7 +9491,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -9523,7 +9518,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -9550,7 +9545,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -9572,7 +9567,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -9594,75 +9589,68 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="T28" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="T29" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="T30" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="T31" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="T32" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
+          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="T33" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
+          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="T34" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
+          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="T35" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
+          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="T36" t="inlineStr">
-        <is>
-          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="T37" t="inlineStr">
         <is>
           <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
@@ -9679,7 +9667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,7 +11424,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11467,16 +11455,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 4LB · 93500000426</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93500000426</t>
+          <t>93500000469</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11487,16 +11475,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93500000469</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11507,16 +11495,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000488</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11527,16 +11515,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>93500000488</t>
+          <t>93500000486</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11547,16 +11535,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000486</t>
+          <t>93500000487</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11567,16 +11555,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000487</t>
+          <t>93500000475</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11587,16 +11575,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93500000475</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11607,16 +11595,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>93500000468</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11627,16 +11615,16 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93500000468</t>
+          <t>93500000467</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11647,16 +11635,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93500000467</t>
+          <t>93500000473</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11667,16 +11655,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>93500000473</t>
+          <t>93500000466</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11687,16 +11675,16 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93500000466</t>
+          <t>93500000419</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11707,12 +11695,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>93500000419</t>
+          <t>93500000420</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -11727,16 +11715,16 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
+          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>93500000420</t>
+          <t>93500000423</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11747,16 +11735,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>93500000423</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11767,16 +11755,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>93500000422</t>
+          <t>93500000434</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11787,16 +11775,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>93500000434</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11807,16 +11795,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000451</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11827,16 +11815,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>93500000451</t>
+          <t>93500000452</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11847,16 +11835,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>93500000452</t>
+          <t>93500000463</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11867,16 +11855,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>93500000463</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11887,16 +11875,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000442</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11907,16 +11895,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>93500000442</t>
+          <t>93500000449</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11927,16 +11915,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>93500000449</t>
+          <t>93500000450</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11947,16 +11935,16 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>93500000450</t>
+          <t>93500000438</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11967,16 +11955,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>93500000438</t>
+          <t>93500000439</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11987,16 +11975,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
+          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93500000439</t>
+          <t>93500000454</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12007,16 +11995,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
+          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93500000454</t>
+          <t>93500000431</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12027,12 +12015,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
+          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93500000431</t>
+          <t>93500000432</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -12047,16 +12035,16 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
+          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93500000432</t>
+          <t>93500000495</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12067,16 +12055,16 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
+          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93500000495</t>
+          <t>93500000496</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12087,36 +12075,36 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
+          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93500000496</t>
+          <t>93504600000</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
+          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93504600000</t>
+          <t>93508280000</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12127,36 +12115,36 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
+          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>93508280000</t>
+          <t>90304010000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
+          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>90304010000</t>
+          <t>90406520000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12167,16 +12155,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
+          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>90406520000</t>
+          <t>90406480000</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12187,16 +12175,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
+          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>90406480000</t>
+          <t>90409360000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12207,16 +12195,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
+          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>90409360000</t>
+          <t>93517020000</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12227,16 +12215,16 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
+          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>93517020000</t>
+          <t>93516960000</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12247,12 +12235,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
+          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>93516960000</t>
+          <t>93516980000</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -12267,12 +12255,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>93516980000</t>
+          <t>93517060000</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -12287,36 +12275,36 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
+          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>93517060000</t>
+          <t>90009660000</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>90009660000</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12327,16 +12315,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PP GATO CTRL URINARIO 85G · 90401421000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>90401421000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12347,16 +12335,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12367,16 +12355,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12387,16 +12375,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12407,16 +12395,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12427,16 +12415,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12447,16 +12435,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12467,16 +12455,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12487,16 +12475,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12507,16 +12495,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12527,16 +12515,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12547,16 +12535,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12567,16 +12555,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93519520000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12587,16 +12575,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>93519520000</t>
+          <t>93519480000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12607,16 +12595,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>93519480000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12627,16 +12615,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90038410000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12647,16 +12635,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>90038410000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12667,16 +12655,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12687,16 +12675,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>90038400000</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12707,16 +12695,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>90038400000</t>
+          <t>90038390000</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12727,16 +12715,16 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>90038390000</t>
+          <t>93519990000</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12747,16 +12735,16 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>93519990000</t>
+          <t>90038570000</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12767,16 +12755,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>90038570000</t>
+          <t>93519970000</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12787,12 +12775,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
+          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>93519970000</t>
+          <t>90401980000</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -12800,23 +12788,23 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>PRO PLAN</t>
+          <t>ROYAL CANIN</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ROYAL CAN BHN SHITZU ADULTO 1.5 KG. · 90401980000</t>
+          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>90401980000</t>
+          <t>90412110000</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12827,16 +12815,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ROYAL CANIN ALIM. KITTEN 36 -2 KG · 90401430000</t>
+          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>90401430000</t>
+          <t>93505490000</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12847,16 +12835,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ROYAL CANIN BHN CHIHUAHUA 1.5KG · 90412110000</t>
+          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>90412110000</t>
+          <t>90006770000</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12867,16 +12855,16 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO 2KG · 93505490000</t>
+          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>93505490000</t>
+          <t>93505710000</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12887,16 +12875,16 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GASTRO JUNIOR 2.5 KG · 90006770000</t>
+          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>90006770000</t>
+          <t>93505700000</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12907,16 +12895,16 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO / RENAL 2KG · 93505710000</t>
+          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>93505710000</t>
+          <t>93505510000</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12927,16 +12915,16 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ROYAL CANIN GATO SIST URINARIO 1.5K · 93505700000</t>
+          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>93505700000</t>
+          <t>90006780000</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12947,16 +12935,16 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HEPATIC 1.5KG · 93505510000</t>
+          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>93505510000</t>
+          <t>90006790000</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12967,16 +12955,16 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROYAL CANIN HIPOALERGENICO RAZA PQ  1KG · 90006780000</t>
+          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>90006780000</t>
+          <t>90404120000</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12987,16 +12975,16 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROYAL CANIN S.UNRINARIO RAZA PQ 1.5 KG · 90006790000</t>
+          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>90006790000</t>
+          <t>93505570000</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13007,16 +12995,16 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SHN MINI PUPPY 2KG · 90404120000</t>
+          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>90404120000</t>
+          <t>90407030000</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13027,16 +13015,16 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ROYAL CANIN SISTEMA URINARIO 2KG · 93505570000</t>
+          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>93505570000</t>
+          <t>90414301000</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13047,72 +13035,72 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ROYALCANIN HIPOALERGENICO 2KG · 90407030000</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>90407030000</t>
+          <t>93511630000</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SHN MINI STARTER M 'N B 1KG · 90414301000</t>
+          <t>D SHED-X SUPLEMENTO NUTRI /PERROS 8 · 90329810000</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>90414301000</t>
+          <t>90329810000</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ROYAL CANIN</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>93511630000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>D SHED-X SUPLEMENTO NUTRI /PERROS 8 · 90329810000</t>
+          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>90329810000</t>
+          <t>90410980000</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -13120,19 +13108,19 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>935096300001</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -13140,85 +13128,65 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
+          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>90410980000</t>
+          <t>93501390000</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
+          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>935096300001</t>
+          <t>93514810000</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
+          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>93501390000</t>
+          <t>93517660000</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
-        <is>
-          <t>TRIUMPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>93514810000</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
-        <v>2</v>
-      </c>
-      <c r="D177" t="inlineStr">
         <is>
           <t>ZOO MED</t>
         </is>
@@ -13227,54 +13195,34 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
+          <t>Sucursal</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>93517660000</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>1</v>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
-        </is>
+          <t>P&amp;G | HOSPITAL PARQUE LEFEVRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>106</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>Inventario al</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>P&amp;G | HOSPITAL PARQUE LEFEVRE</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Inventario al</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>20.10.2026</t>
+          <t>21.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/106.xlsx
+++ b/plantillas/106.xlsx
@@ -15,7 +15,7 @@
     <definedName name="MARCA_1">Listas!$D$2:$D$10</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$6</definedName>
     <definedName name="MARCA_3">Listas!$F$2:$F$4</definedName>
-    <definedName name="MARCA_4">Listas!$G$2:$G$25</definedName>
+    <definedName name="MARCA_4">Listas!$G$2:$G$24</definedName>
     <definedName name="MARCA_5">Listas!$H$2:$H$2</definedName>
     <definedName name="MARCA_6">Listas!$I$2:$I$4</definedName>
     <definedName name="MARCA_7">Listas!$J$2:$J$7</definedName>
@@ -27,11 +27,11 @@
     <definedName name="MARCA_13">Listas!$P$2:$P$3</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$4</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$4</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$19</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$18</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$36</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$3</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$9</definedName>
-    <definedName name="MARCA_20">Listas!$W$2:$W$26</definedName>
+    <definedName name="MARCA_20">Listas!$W$2:$W$28</definedName>
     <definedName name="MARCA_21">Listas!$X$2:$X$14</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$2</definedName>
     <definedName name="MARCA_23">Listas!$Z$2:$Z$2</definedName>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
+          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
+          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
+          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
+          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
+          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
+          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
+          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
+          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -9013,12 +9013,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
+          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -9060,12 +9060,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
+          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
+          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
+          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
+          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
+          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
+          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
+          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -9208,12 +9208,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
+          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
+          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
+          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
+          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
     </row>
@@ -9277,12 +9277,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
+          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
+          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
+          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
+          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9341,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
+          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
+          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
+          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -9388,7 +9383,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9400,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
+          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -9415,7 +9410,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9427,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
+          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -9442,7 +9437,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9454,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
+          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -9469,7 +9464,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9481,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
+          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -9496,7 +9491,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9508,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
+          <t>CS SNACK SAVORY STICKS TOCINO 5OZ · 93514670000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -9523,7 +9518,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
     </row>
@@ -9538,11 +9533,6 @@
           <t>MARCA_24</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>CS SNACK SAVORY STICKS TOCINO 5OZ · 93514670000</t>
-        </is>
-      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
@@ -9550,7 +9540,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9562,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
+          <t>PROPLAN GATO SENIOR POLLO/ARROZ 3KG · 93519990000</t>
         </is>
       </c>
     </row>
@@ -9592,11 +9582,21 @@
           <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>PROPLAN URINARY GATO ADULTO 1.5KG MX · 90038570000</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="T28" t="inlineStr">
         <is>
           <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>PROPLAN URINARY OPTITRACT 3KG · 93519970000</t>
         </is>
       </c>
     </row>
@@ -10035,16 +10035,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CS ALIM LATA POLLO/GATO MATURE 5.5 · 93511250000</t>
+          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>93511250000</t>
+          <t>93511170000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -10055,16 +10055,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
+          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93511170000</t>
+          <t>93511160000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -10075,16 +10075,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/CACHORRO 13OZ · 93511160000</t>
+          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93511160000</t>
+          <t>93500000261</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE POLLO EN SALSA 5.5O · 93500000261</t>
+          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93500000261</t>
+          <t>93500000263</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -10115,12 +10115,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CS CLASSIC GATO PATE SALMON EN SALSA 5.5 · 93500000263</t>
+          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>93500000263</t>
+          <t>93511070000</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -10135,16 +10135,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/ADULTO 4.5LB · 93511070000</t>
+          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93511070000</t>
+          <t>93511130000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -10155,16 +10155,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CS CLASSIC POLLO P/MATURE 4.5LB · 93511130000</t>
+          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93511130000</t>
+          <t>93500000252</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -10175,16 +10175,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CS GATO CTRL PESO Y SENIOR 4.5LB · 93500000252</t>
+          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>93500000252</t>
+          <t>93500000254</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -10195,12 +10195,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CS GATO SALMON Y ARROZ 4.5LB · 93500000254</t>
+          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93500000254</t>
+          <t>93500000257</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -10215,12 +10215,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CS GF PERRO LATA PAVO, CAMOTE 13OZ · 93500000257</t>
+          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93500000257</t>
+          <t>93500000259</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -10235,16 +10235,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PAVO, SALMON 13OZ · 93500000259</t>
+          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93500000259</t>
+          <t>93500000258</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10255,16 +10255,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CS GF PERRO POLLO, PESCADO 13OZ · 93500000258</t>
+          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93500000258</t>
+          <t>93514460000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -10275,12 +10275,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON P/PERRO 4 LB · 93514460000</t>
+          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93514460000</t>
+          <t>93514480000</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -10295,16 +10295,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
+          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93514480000</t>
+          <t>93500000248</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10315,16 +10315,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CS PERR CTRL PESO ARROZ, POLLO, PAVO 4.5 · 93500000248</t>
+          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93500000248</t>
+          <t>93514390000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10335,16 +10335,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY M MANI /PERRO 12OZ · 93514390000</t>
+          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93514390000</t>
+          <t>93511270000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10355,16 +10355,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
+          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93511270000</t>
+          <t>93514380000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10375,16 +10375,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY TOCINO /PERRO 12OZ · 93514380000</t>
+          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93514380000</t>
+          <t>93514410000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10395,16 +10395,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY CARNE P/PERRO 6OZ · 93514410000</t>
+          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93514410000</t>
+          <t>93514420000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10415,16 +10415,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY POLLO P/PERRO 6OZ · 93514420000</t>
+          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93514420000</t>
+          <t>93514660000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10435,12 +10435,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS CARNE 5OZ · 93514660000</t>
+          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93514660000</t>
+          <t>93514680000</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -10455,12 +10455,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS PATO 5OZ · 93514680000</t>
+          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93514680000</t>
+          <t>93514650000</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -10475,12 +10475,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS POLLO 5OZ · 93514650000</t>
+          <t>CS SNACK SAVORY STICKS TOCINO 5OZ · 93514670000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93514650000</t>
+          <t>93514670000</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -10495,56 +10495,56 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CS SNACK SAVORY STICKS TOCINO 5OZ · 93514670000</t>
+          <t>D CUNIPIC CANARIOS 1KG · 93517250000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>93514670000</t>
+          <t>93517250000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CHICKEN SOUP</t>
+          <t>CUNIPIC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D CUNIPIC CANARIOS 1KG · 93517250000</t>
+          <t>D ERA SYBARITE LATA ATUN/CERDO 400G · 93519110000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93517250000</t>
+          <t>93519110000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CUNIPIC</t>
+          <t>ERA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D ERA SYBARITE LATA ATUN/CERDO 400G · 93519110000</t>
+          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93519110000</t>
+          <t>93519090000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10555,16 +10555,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATA CACHORROS 400G · 93519090000</t>
+          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93519090000</t>
+          <t>93519100000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10575,36 +10575,36 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ERA SYBARITE LATAPOLLO/PESCADO 400G · 93519100000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93519100000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ERA</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90312680000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10615,16 +10615,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ESBILAC PAPILLA P CACHORROS 14 OZ. · 90312680000</t>
+          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90312680000</t>
+          <t>90404010000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10635,12 +10635,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KMR PAPILLA P GATITOS 2STEP 14 OZ. · 90404010000</t>
+          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90404010000</t>
+          <t>90330330000</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -10655,16 +10655,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PA VITAM/MINERALES GEL P/GATO · 90330330000</t>
+          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90330330000</t>
+          <t>90330310000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10675,16 +10675,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PA VITAMINA EN GEL CALORIAS P/GATO · 90330310000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90330310000</t>
+          <t>90308700000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10695,32 +10695,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+          <t>EUK DOG LARGE SENIOR   3 Kg (6.61 lbs) · 90018640000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90308700000</t>
+          <t>90018640000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EUKANUBA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EUK DOG LARGE SENIOR   3 Kg (6.61 lbs) · 90018640000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90018640000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -10728,63 +10728,63 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93500000142</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GRANDMA MAE'S</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GM COUNT NAT ESTOMAG SENSIBLE/ PERRO 4LB · 93500000142</t>
+          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>93500000142</t>
+          <t>93507510001</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GRANDMA MAE'S</t>
+          <t>HILL'S</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SD ADULTO ESTOMAGO/PIEL SENSIBLE 4LB · 93507510001</t>
+          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>93507510001</t>
+          <t>93509840000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10795,32 +10795,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SD LATA CACHORRO POLLO 13OZ · 93509840000</t>
+          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>93509840000</t>
+          <t>93518150000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HILL'S</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KT ALIM TIMOTHY SELECT CONEJOS 3.5 · 93518150000</t>
+          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>93518150000</t>
+          <t>90405030000</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -10835,12 +10835,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KT ALIM. FORTI DIET CONEJO 5 LB · 90405030000</t>
+          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90405030000</t>
+          <t>90310300000</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -10848,19 +10848,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KORDON VITAMINA C PARA COBAYOS 2OZ · 90310300000</t>
+          <t>KORDON VITAMINAS P COBAYOS 2 OZ · 90720790000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90310300000</t>
+          <t>90720790000</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -10875,36 +10875,36 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS P COBAYOS 2 OZ · 90720790000</t>
+          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90720790000</t>
+          <t>90322660000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIRRAPEL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 120 ML · 90322660000</t>
+          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90322660000</t>
+          <t>90322670000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10915,16 +10915,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MIRRAPEL CACHORROS 236 ML · 90322670000</t>
+          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90322670000</t>
+          <t>90301720000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10935,36 +10935,36 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90415960000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -10975,16 +10975,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10995,32 +10995,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90328330000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D NV EXTRA SOPORTE/ARTICULACION 250U · 90328330000</t>
+          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90328330000</t>
+          <t>93518700000</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -11035,16 +11035,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>D NV PASTILLA MASTICABLE P/VEJIGA 60U · 93518700000</t>
+          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>93518700000</t>
+          <t>90332570000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -11055,16 +11055,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D NV SUPLEMEN HONGOS P/SISTEMA INMUNE · 90332570000</t>
+          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>90332570000</t>
+          <t>90328650000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -11075,16 +11075,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D NV SUPLEMENTO ANTI COPROFAGIA 500 · 90328650000</t>
+          <t>D NV SUPLEMENTO TRANQUILIZANTE 180 UD · 93518710000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90328650000</t>
+          <t>93518710000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -11095,16 +11095,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>D NV SUPLEMENTO TRANQUILIZANTE 180 UD · 93518710000</t>
+          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>93518710000</t>
+          <t>90328760000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -11115,16 +11115,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D NV TABLET PERR SENIOR MALESTAR/DOL · 90328760000</t>
+          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90328760000</t>
+          <t>90327410000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -11135,16 +11135,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D NV VITAMINA P/ TRACTO DIGESTIVO 60U · 90328340000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>90328340000</t>
+          <t>90327780000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11155,16 +11155,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D NV VITAMINAS LEVADURA/AJO 100UD · 90327410000</t>
+          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>90327410000</t>
+          <t>90328050000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -11175,16 +11175,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 1 · 90327780000</t>
+          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>90327780000</t>
+          <t>90328300000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -11195,16 +11195,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NV GLUCOSAMINA MASTICABLE NIVEL 2 · 90328050000</t>
+          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>90328050000</t>
+          <t>90327640000</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -11215,16 +11215,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NV HIP N JOINT MASTICABLE 120UD · 90328300000</t>
+          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>90328300000</t>
+          <t>90328780000</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -11235,16 +11235,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NV PAST MAST CON ARANDANO P/PERRO60 · 90327640000</t>
+          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>90327640000</t>
+          <t>90328700000</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11255,16 +11255,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NV SENIOR PAST/ARTICULACIONES 120UD · 90328780000</t>
+          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>90328780000</t>
+          <t>90328740000</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11275,16 +11275,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/GATOS 60UD · 90328700000</t>
+          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>90328700000</t>
+          <t>90328770000</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11295,16 +11295,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST P/PERRO 70 · 90328740000</t>
+          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>90328740000</t>
+          <t>90328860000</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11315,12 +11315,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTE MAST PERRO SENIOR · 90328770000</t>
+          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>90328770000</t>
+          <t>90328840000</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -11335,12 +11335,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NV VITAMINA MAST PERRO SENIOR 60U · 90328860000</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>90328860000</t>
+          <t>93500000429</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -11348,43 +11348,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NV VITAMINA P/CACHORRO ALIENTO 70 U · 90328840000</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>90328840000</t>
+          <t>93500000460</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>93500000429</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11395,16 +11395,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 12LB · 93500000460</t>
+          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>93500000460</t>
+          <t>93500000425</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11415,16 +11415,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000469</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11435,16 +11435,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>NS CACHORRO SM MD POLLO Y ARROZ 12LB · 93500000425</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>93500000425</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11455,16 +11455,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO POLLO 13OZ · 93500000469</t>
+          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93500000469</t>
+          <t>93500000488</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11475,16 +11475,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
+          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93500000471</t>
+          <t>93500000486</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11495,16 +11495,16 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLL PAV CORD PESC 5 · 93500000488</t>
+          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93500000488</t>
+          <t>93500000487</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11515,16 +11515,16 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO 5.5 OZ · 93500000486</t>
+          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>93500000486</t>
+          <t>93500000475</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11535,16 +11535,16 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NS LATA GATO GATITO POLLO PAVO CORDERO 5 · 93500000487</t>
+          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000487</t>
+          <t>93500000472</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11555,16 +11555,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO MARISCOS 13OZ · 93500000475</t>
+          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000475</t>
+          <t>93500000468</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11575,16 +11575,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NS LATA GF PERRO POLLO 13OZ · 93500000472</t>
+          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93500000472</t>
+          <t>93500000467</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11595,16 +11595,16 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO 13OZ · 93500000468</t>
+          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93500000468</t>
+          <t>93500000473</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11615,12 +11615,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>NS LATA PERRO CORDERO Y PESCADO 13OZ · 93500000467</t>
+          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93500000467</t>
+          <t>93500000466</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11635,16 +11635,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NS LATA PERRO GF HEARTLAND SELECT 13OZ · 93500000473</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93500000473</t>
+          <t>93500000419</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11655,16 +11655,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NS LATA PERRO POLLO Y ARROZ 13OZ · 93500000466</t>
+          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>93500000466</t>
+          <t>93500000420</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11675,16 +11675,16 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 12LB · 93500000419</t>
+          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>93500000419</t>
+          <t>93500000423</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11695,16 +11695,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NS PERRO ADULT POLLO Y ARROZ 4LB · 93500000420</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>93500000420</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11715,12 +11715,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO POLLO Y ARROZ 26LB · 93500000423</t>
+          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>93500000423</t>
+          <t>93500000434</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -11735,16 +11735,16 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>93500000422</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11755,16 +11755,16 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 12LB · 93500000434</t>
+          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>93500000434</t>
+          <t>93500000451</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11775,16 +11775,16 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000452</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11795,16 +11795,16 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 12LB · 93500000451</t>
+          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>93500000451</t>
+          <t>93500000463</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11815,16 +11815,16 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NS PERRO CTRL PESO GF 4LB · 93500000452</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>93500000452</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11835,16 +11835,16 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 12LB · 93500000463</t>
+          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>93500000463</t>
+          <t>93500000442</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11855,16 +11855,16 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000449</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11875,16 +11875,16 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>NS PERRO GF POLLO Y GUISANTE 4LB · 93500000442</t>
+          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>93500000442</t>
+          <t>93500000450</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11895,16 +11895,16 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 12L · 93500000449</t>
+          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>93500000449</t>
+          <t>93500000438</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11915,16 +11915,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NS PERRO GF RZ PQNA POLLO GUISANTE 4LB · 93500000450</t>
+          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>93500000450</t>
+          <t>93500000439</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11935,12 +11935,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 12LB · 93500000438</t>
+          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>93500000438</t>
+          <t>93500000454</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -11955,16 +11955,16 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NS PERRO PAVO Y ARROZ 4LB · 93500000439</t>
+          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>93500000439</t>
+          <t>93500000431</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11975,16 +11975,16 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NS PERRO SENIOR GF 12LB · 93500000454</t>
+          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>93500000454</t>
+          <t>93500000432</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11995,16 +11995,16 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 12LB · 93500000431</t>
+          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>93500000431</t>
+          <t>93500000495</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12015,16 +12015,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NS SENIOR POLLO Y ARROZ 4LB · 93500000432</t>
+          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>93500000432</t>
+          <t>93500000496</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12035,32 +12035,32 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NS SNACK ARÁNDANO Y ALMENDRA 6OZ · 93500000495</t>
+          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>93500000495</t>
+          <t>93504600000</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NS SNACK GF BOCADOS GDES CARNE 14OZ · 93500000496</t>
+          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>93500000496</t>
+          <t>93508280000</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -12068,63 +12068,63 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NY SNACK DENTAL FILET MIGNON SM28 · 93504600000</t>
+          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>93504600000</t>
+          <t>90304010000</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO PETITE CARNE ASADA · 93508280000</t>
+          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>93508280000</t>
+          <t>90406520000</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>PRESCRIPTION DIET</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SD CANINE I/D 8.5 LB · 90304010000</t>
+          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>90304010000</t>
+          <t>90406480000</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12135,16 +12135,16 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SD LATA CANINE I/D/12/ 13 OZ. · 90406520000</t>
+          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>90406520000</t>
+          <t>90409360000</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12155,16 +12155,16 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SD LATA CANINE L/D12/ 13 OZ. · 90406480000</t>
+          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>90406480000</t>
+          <t>93517020000</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12175,16 +12175,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SD LATA FELINE K/D 5.5OZ · 90409360000</t>
+          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>90409360000</t>
+          <t>93516960000</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12195,16 +12195,16 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SD PD CANINDE C/D LATA 12OZ · 93517020000</t>
+          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>93517020000</t>
+          <t>93516980000</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12215,12 +12215,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SD PD CANINE K/D 3.3LB · 93516960000</t>
+          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>93516960000</t>
+          <t>93517060000</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -12235,56 +12235,56 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SD PD CANINE W/D 3.3LB · 93516980000</t>
+          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>93516980000</t>
+          <t>90009660000</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SD PF GATOS C/D LATA 5.5OZ · 93517060000</t>
+          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>93517060000</t>
+          <t>90009650000</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PRESCRIPTION DIET</t>
+          <t>PRO PLAN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>M PP GATO FORTI-FLORA 30X1.06OZ · 90009660000</t>
+          <t>PP GATO LATA SOPORTE URINARIO 5.5OZ · 93519420000</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>90009660000</t>
+          <t>93519420000</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12295,16 +12295,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>M PP PERROS FORTI-FLORA UNIDAD 1.06OZ · 90009650000</t>
+          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>90009650000</t>
+          <t>93519430000</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12315,16 +12315,16 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PP GATO NF ADVANCE RINONES 3.15LB · 93519430000</t>
+          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>93519430000</t>
+          <t>93519440000</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12335,16 +12335,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PP GATO NF LATA ADVANCE RINONES 5.5 · 93519440000</t>
+          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>93519440000</t>
+          <t>93519410000</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12355,16 +12355,16 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PP GATO SOPORTE URINARIO 6LB · 93519410000</t>
+          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>93519410000</t>
+          <t>93519460000</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12375,16 +12375,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PP GATOS LATA VET EN GASTRO 5.5OZ · 93519460000</t>
+          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>93519460000</t>
+          <t>93519450000</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12395,16 +12395,16 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PP GATOS VET HYDROLYZED 4LB · 93519450000</t>
+          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>93519450000</t>
+          <t>93519540000</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12415,16 +12415,16 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PP PERROS EN GASTRO 6LB · 93519540000</t>
+          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>93519540000</t>
+          <t>93519470000</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12435,16 +12435,16 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PP PERROS FORTI-FLORA 30X1.06OZ · 93519470000</t>
+          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>93519470000</t>
+          <t>93519500000</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12455,16 +12455,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PP PERROS HYDROLYZED 6LB · 93519500000</t>
+          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>93519500000</t>
+          <t>93519550000</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12475,16 +12475,16 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PP PERROS LATA GASTRO 13.4OZ · 93519550000</t>
+          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>93519550000</t>
+          <t>93519510000</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12495,16 +12495,16 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PP PERROS LATA HYDROLYZED 13.3OZ · 93519510000</t>
+          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>93519510000</t>
+          <t>93519490000</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12515,16 +12515,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOBREPESO 13.3OZ · 93519490000</t>
+          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>93519490000</t>
+          <t>93519530000</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12535,16 +12535,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PP PERROS LATA SOPORTE RINONES 13.3 · 93519530000</t>
+          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>93519530000</t>
+          <t>93519520000</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12555,16 +12555,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PP PERROS NF SOPORTE RINONES 6LB · 93519520000</t>
+          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>93519520000</t>
+          <t>93519480000</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12575,16 +12575,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PP PERROS SOBREPESO 6LB · 93519480000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>93519480000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12595,16 +12595,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90038410000</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12615,16 +12615,16 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>90038410000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12635,16 +12635,16 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12655,16 +12655,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>90038400000</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12675,16 +12675,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 13.3OZ · 90038400000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90038400000</t>
+          <t>90038390000</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12695,16 +12695,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
+          <t>PROPLAN GATO ESTERILIZADO SALMON 3K · 93519980000</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>90038390000</t>
+          <t>93519980000</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>21.10.2026</t>
+          <t>23.10.2026</t>
         </is>
       </c>
     </row>
